--- a/Atana-Backlog-AzureDevOps-v1.xlsx
+++ b/Atana-Backlog-AzureDevOps-v1.xlsx
@@ -5970,199 +5970,4 @@
   <autoFilter ref="A1:K48"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101008E3AE2BAD2C6FA4D8B4D95CE89FC31A3" ma:contentTypeVersion="8" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="a2ce85c62cd7e9a608298e998330aeb7">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="ae81e17b-11c2-44ae-89e9-9ad5f5ff8880" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="1504f635df8bfa7d9525024d2d10bc95" ns2:_="">
-    <xsd:import namespace="ae81e17b-11c2-44ae-89e9-9ad5f5ff8880"/>
-    <xsd:element name="properties">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element name="documentManagement">
-            <xsd:complexType>
-              <xsd:all>
-                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
-              </xsd:all>
-            </xsd:complexType>
-          </xsd:element>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="ae81e17b-11c2-44ae-89e9-9ad5f5ff8880" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceSearchProperties" ma:index="10" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="11" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="13" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="c4ac2493-9f1f-4345-86a0-c36146f38f1d" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="14" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
-    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
-    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
-    <xsd:element name="coreProperties" type="CT_coreProperties"/>
-    <xsd:complexType name="CT_coreProperties">
-      <xsd:all>
-        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
-        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
-          <xsd:annotation>
-            <xsd:documentation>
-                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
-                    </xsd:documentation>
-          </xsd:annotation>
-        </xsd:element>
-        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-      </xsd:all>
-    </xsd:complexType>
-  </xsd:schema>
-  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
-    <xs:element name="Person">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:DisplayName" minOccurs="0"/>
-          <xs:element ref="pc:AccountId" minOccurs="0"/>
-          <xs:element ref="pc:AccountType" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="DisplayName" type="xs:string"/>
-    <xs:element name="AccountId" type="xs:string"/>
-    <xs:element name="AccountType" type="xs:string"/>
-    <xs:element name="BDCAssociatedEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-        <xs:attribute ref="pc:EntityNamespace"/>
-        <xs:attribute ref="pc:EntityName"/>
-        <xs:attribute ref="pc:SystemInstanceName"/>
-        <xs:attribute ref="pc:AssociationName"/>
-      </xs:complexType>
-    </xs:element>
-    <xs:attribute name="EntityNamespace" type="xs:string"/>
-    <xs:attribute name="EntityName" type="xs:string"/>
-    <xs:attribute name="SystemInstanceName" type="xs:string"/>
-    <xs:attribute name="AssociationName" type="xs:string"/>
-    <xs:element name="BDCEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
-          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
-          <xs:element ref="pc:EntityId1" minOccurs="0"/>
-          <xs:element ref="pc:EntityId2" minOccurs="0"/>
-          <xs:element ref="pc:EntityId3" minOccurs="0"/>
-          <xs:element ref="pc:EntityId4" minOccurs="0"/>
-          <xs:element ref="pc:EntityId5" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="EntityDisplayName" type="xs:string"/>
-    <xs:element name="EntityInstanceReference" type="xs:string"/>
-    <xs:element name="EntityId1" type="xs:string"/>
-    <xs:element name="EntityId2" type="xs:string"/>
-    <xs:element name="EntityId3" type="xs:string"/>
-    <xs:element name="EntityId4" type="xs:string"/>
-    <xs:element name="EntityId5" type="xs:string"/>
-    <xs:element name="Terms">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermInfo">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermName" minOccurs="0"/>
-          <xs:element ref="pc:TermId" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermName" type="xs:string"/>
-    <xs:element name="TermId" type="xs:string"/>
-  </xs:schema>
-</ct:contentTypeSchema>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="ae81e17b-11c2-44ae-89e9-9ad5f5ff8880">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1CEC75D2-1CE6-4054-BCE0-DAB23486F0DC}"/>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7DD4CF7F-CA40-4B94-AB27-6B52DF7061FB}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1448D410-B027-4DB1-B374-4FA625F43374}"/>
 </file>
--- a/Atana-Backlog-AzureDevOps-v1.xlsx
+++ b/Atana-Backlog-AzureDevOps-v1.xlsx
@@ -5970,4 +5970,199 @@
   <autoFilter ref="A1:K48"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101008E3AE2BAD2C6FA4D8B4D95CE89FC31A3" ma:contentTypeVersion="8" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="a2ce85c62cd7e9a608298e998330aeb7">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="ae81e17b-11c2-44ae-89e9-9ad5f5ff8880" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="1504f635df8bfa7d9525024d2d10bc95" ns2:_="">
+    <xsd:import namespace="ae81e17b-11c2-44ae-89e9-9ad5f5ff8880"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="ae81e17b-11c2-44ae-89e9-9ad5f5ff8880" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="10" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="11" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="13" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="c4ac2493-9f1f-4345-86a0-c36146f38f1d" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="14" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="ae81e17b-11c2-44ae-89e9-9ad5f5ff8880">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B7DBD657-C208-409E-B023-834DB7A88DAF}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C0C1BFED-3E3F-40F0-8EE4-8D5D93A625BB}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6FE68EFC-499C-4858-B2F7-7F586332CFCE}"/>
 </file>
--- a/Atana-Backlog-AzureDevOps-v1.xlsx
+++ b/Atana-Backlog-AzureDevOps-v1.xlsx
@@ -5970,199 +5970,4 @@
   <autoFilter ref="A1:K48"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101008E3AE2BAD2C6FA4D8B4D95CE89FC31A3" ma:contentTypeVersion="8" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="a2ce85c62cd7e9a608298e998330aeb7">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="ae81e17b-11c2-44ae-89e9-9ad5f5ff8880" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="1504f635df8bfa7d9525024d2d10bc95" ns2:_="">
-    <xsd:import namespace="ae81e17b-11c2-44ae-89e9-9ad5f5ff8880"/>
-    <xsd:element name="properties">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element name="documentManagement">
-            <xsd:complexType>
-              <xsd:all>
-                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
-              </xsd:all>
-            </xsd:complexType>
-          </xsd:element>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="ae81e17b-11c2-44ae-89e9-9ad5f5ff8880" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceSearchProperties" ma:index="10" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="11" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="13" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="c4ac2493-9f1f-4345-86a0-c36146f38f1d" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="14" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
-    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
-    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
-    <xsd:element name="coreProperties" type="CT_coreProperties"/>
-    <xsd:complexType name="CT_coreProperties">
-      <xsd:all>
-        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
-        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
-          <xsd:annotation>
-            <xsd:documentation>
-                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
-                    </xsd:documentation>
-          </xsd:annotation>
-        </xsd:element>
-        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-      </xsd:all>
-    </xsd:complexType>
-  </xsd:schema>
-  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
-    <xs:element name="Person">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:DisplayName" minOccurs="0"/>
-          <xs:element ref="pc:AccountId" minOccurs="0"/>
-          <xs:element ref="pc:AccountType" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="DisplayName" type="xs:string"/>
-    <xs:element name="AccountId" type="xs:string"/>
-    <xs:element name="AccountType" type="xs:string"/>
-    <xs:element name="BDCAssociatedEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-        <xs:attribute ref="pc:EntityNamespace"/>
-        <xs:attribute ref="pc:EntityName"/>
-        <xs:attribute ref="pc:SystemInstanceName"/>
-        <xs:attribute ref="pc:AssociationName"/>
-      </xs:complexType>
-    </xs:element>
-    <xs:attribute name="EntityNamespace" type="xs:string"/>
-    <xs:attribute name="EntityName" type="xs:string"/>
-    <xs:attribute name="SystemInstanceName" type="xs:string"/>
-    <xs:attribute name="AssociationName" type="xs:string"/>
-    <xs:element name="BDCEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
-          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
-          <xs:element ref="pc:EntityId1" minOccurs="0"/>
-          <xs:element ref="pc:EntityId2" minOccurs="0"/>
-          <xs:element ref="pc:EntityId3" minOccurs="0"/>
-          <xs:element ref="pc:EntityId4" minOccurs="0"/>
-          <xs:element ref="pc:EntityId5" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="EntityDisplayName" type="xs:string"/>
-    <xs:element name="EntityInstanceReference" type="xs:string"/>
-    <xs:element name="EntityId1" type="xs:string"/>
-    <xs:element name="EntityId2" type="xs:string"/>
-    <xs:element name="EntityId3" type="xs:string"/>
-    <xs:element name="EntityId4" type="xs:string"/>
-    <xs:element name="EntityId5" type="xs:string"/>
-    <xs:element name="Terms">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermInfo">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermName" minOccurs="0"/>
-          <xs:element ref="pc:TermId" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermName" type="xs:string"/>
-    <xs:element name="TermId" type="xs:string"/>
-  </xs:schema>
-</ct:contentTypeSchema>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="ae81e17b-11c2-44ae-89e9-9ad5f5ff8880">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B7DBD657-C208-409E-B023-834DB7A88DAF}"/>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C0C1BFED-3E3F-40F0-8EE4-8D5D93A625BB}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6FE68EFC-499C-4858-B2F7-7F586332CFCE}"/>
 </file>
--- a/Atana-Backlog-AzureDevOps-v1.xlsx
+++ b/Atana-Backlog-AzureDevOps-v1.xlsx
@@ -5970,4 +5970,199 @@
   <autoFilter ref="A1:K48"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101008E3AE2BAD2C6FA4D8B4D95CE89FC31A3" ma:contentTypeVersion="8" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="a2ce85c62cd7e9a608298e998330aeb7">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="ae81e17b-11c2-44ae-89e9-9ad5f5ff8880" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="1504f635df8bfa7d9525024d2d10bc95" ns2:_="">
+    <xsd:import namespace="ae81e17b-11c2-44ae-89e9-9ad5f5ff8880"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="ae81e17b-11c2-44ae-89e9-9ad5f5ff8880" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="10" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="11" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="13" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="c4ac2493-9f1f-4345-86a0-c36146f38f1d" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="14" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="ae81e17b-11c2-44ae-89e9-9ad5f5ff8880">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3C28B829-3E95-4841-B87A-FB01E8E002FE}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CFDC846D-05FC-4270-961F-514CC567D53A}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7ACDA3D9-8433-48A9-9893-9D42345E5622}"/>
 </file>
--- a/Atana-Backlog-AzureDevOps-v1.xlsx
+++ b/Atana-Backlog-AzureDevOps-v1.xlsx
@@ -5970,199 +5970,4 @@
   <autoFilter ref="A1:K48"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101008E3AE2BAD2C6FA4D8B4D95CE89FC31A3" ma:contentTypeVersion="8" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="a2ce85c62cd7e9a608298e998330aeb7">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="ae81e17b-11c2-44ae-89e9-9ad5f5ff8880" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="1504f635df8bfa7d9525024d2d10bc95" ns2:_="">
-    <xsd:import namespace="ae81e17b-11c2-44ae-89e9-9ad5f5ff8880"/>
-    <xsd:element name="properties">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element name="documentManagement">
-            <xsd:complexType>
-              <xsd:all>
-                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
-              </xsd:all>
-            </xsd:complexType>
-          </xsd:element>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="ae81e17b-11c2-44ae-89e9-9ad5f5ff8880" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceSearchProperties" ma:index="10" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="11" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="13" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="c4ac2493-9f1f-4345-86a0-c36146f38f1d" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="14" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
-    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
-    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
-    <xsd:element name="coreProperties" type="CT_coreProperties"/>
-    <xsd:complexType name="CT_coreProperties">
-      <xsd:all>
-        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
-        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
-          <xsd:annotation>
-            <xsd:documentation>
-                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
-                    </xsd:documentation>
-          </xsd:annotation>
-        </xsd:element>
-        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-      </xsd:all>
-    </xsd:complexType>
-  </xsd:schema>
-  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
-    <xs:element name="Person">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:DisplayName" minOccurs="0"/>
-          <xs:element ref="pc:AccountId" minOccurs="0"/>
-          <xs:element ref="pc:AccountType" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="DisplayName" type="xs:string"/>
-    <xs:element name="AccountId" type="xs:string"/>
-    <xs:element name="AccountType" type="xs:string"/>
-    <xs:element name="BDCAssociatedEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-        <xs:attribute ref="pc:EntityNamespace"/>
-        <xs:attribute ref="pc:EntityName"/>
-        <xs:attribute ref="pc:SystemInstanceName"/>
-        <xs:attribute ref="pc:AssociationName"/>
-      </xs:complexType>
-    </xs:element>
-    <xs:attribute name="EntityNamespace" type="xs:string"/>
-    <xs:attribute name="EntityName" type="xs:string"/>
-    <xs:attribute name="SystemInstanceName" type="xs:string"/>
-    <xs:attribute name="AssociationName" type="xs:string"/>
-    <xs:element name="BDCEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
-          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
-          <xs:element ref="pc:EntityId1" minOccurs="0"/>
-          <xs:element ref="pc:EntityId2" minOccurs="0"/>
-          <xs:element ref="pc:EntityId3" minOccurs="0"/>
-          <xs:element ref="pc:EntityId4" minOccurs="0"/>
-          <xs:element ref="pc:EntityId5" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="EntityDisplayName" type="xs:string"/>
-    <xs:element name="EntityInstanceReference" type="xs:string"/>
-    <xs:element name="EntityId1" type="xs:string"/>
-    <xs:element name="EntityId2" type="xs:string"/>
-    <xs:element name="EntityId3" type="xs:string"/>
-    <xs:element name="EntityId4" type="xs:string"/>
-    <xs:element name="EntityId5" type="xs:string"/>
-    <xs:element name="Terms">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermInfo">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermName" minOccurs="0"/>
-          <xs:element ref="pc:TermId" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermName" type="xs:string"/>
-    <xs:element name="TermId" type="xs:string"/>
-  </xs:schema>
-</ct:contentTypeSchema>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="ae81e17b-11c2-44ae-89e9-9ad5f5ff8880">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3C28B829-3E95-4841-B87A-FB01E8E002FE}"/>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CFDC846D-05FC-4270-961F-514CC567D53A}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7ACDA3D9-8433-48A9-9893-9D42345E5622}"/>
 </file>
--- a/Atana-Backlog-AzureDevOps-v1.xlsx
+++ b/Atana-Backlog-AzureDevOps-v1.xlsx
@@ -5970,4 +5970,199 @@
   <autoFilter ref="A1:K48"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101008E3AE2BAD2C6FA4D8B4D95CE89FC31A3" ma:contentTypeVersion="8" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="a2ce85c62cd7e9a608298e998330aeb7">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="ae81e17b-11c2-44ae-89e9-9ad5f5ff8880" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="1504f635df8bfa7d9525024d2d10bc95" ns2:_="">
+    <xsd:import namespace="ae81e17b-11c2-44ae-89e9-9ad5f5ff8880"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="ae81e17b-11c2-44ae-89e9-9ad5f5ff8880" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="10" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="11" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="13" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="c4ac2493-9f1f-4345-86a0-c36146f38f1d" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="14" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="ae81e17b-11c2-44ae-89e9-9ad5f5ff8880">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1B067714-3971-4234-AABC-C408078E1CBC}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2B0CDE59-B503-44BD-99FC-3772E552C782}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F1135BEA-392D-4B5C-B352-5EC7B079E2C0}"/>
 </file>
--- a/Atana-Backlog-AzureDevOps-v1.xlsx
+++ b/Atana-Backlog-AzureDevOps-v1.xlsx
@@ -5970,199 +5970,4 @@
   <autoFilter ref="A1:K48"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101008E3AE2BAD2C6FA4D8B4D95CE89FC31A3" ma:contentTypeVersion="8" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="a2ce85c62cd7e9a608298e998330aeb7">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="ae81e17b-11c2-44ae-89e9-9ad5f5ff8880" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="1504f635df8bfa7d9525024d2d10bc95" ns2:_="">
-    <xsd:import namespace="ae81e17b-11c2-44ae-89e9-9ad5f5ff8880"/>
-    <xsd:element name="properties">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element name="documentManagement">
-            <xsd:complexType>
-              <xsd:all>
-                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
-              </xsd:all>
-            </xsd:complexType>
-          </xsd:element>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="ae81e17b-11c2-44ae-89e9-9ad5f5ff8880" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceSearchProperties" ma:index="10" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="11" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="13" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="c4ac2493-9f1f-4345-86a0-c36146f38f1d" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="14" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
-    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
-    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
-    <xsd:element name="coreProperties" type="CT_coreProperties"/>
-    <xsd:complexType name="CT_coreProperties">
-      <xsd:all>
-        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
-        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
-          <xsd:annotation>
-            <xsd:documentation>
-                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
-                    </xsd:documentation>
-          </xsd:annotation>
-        </xsd:element>
-        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-      </xsd:all>
-    </xsd:complexType>
-  </xsd:schema>
-  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
-    <xs:element name="Person">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:DisplayName" minOccurs="0"/>
-          <xs:element ref="pc:AccountId" minOccurs="0"/>
-          <xs:element ref="pc:AccountType" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="DisplayName" type="xs:string"/>
-    <xs:element name="AccountId" type="xs:string"/>
-    <xs:element name="AccountType" type="xs:string"/>
-    <xs:element name="BDCAssociatedEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-        <xs:attribute ref="pc:EntityNamespace"/>
-        <xs:attribute ref="pc:EntityName"/>
-        <xs:attribute ref="pc:SystemInstanceName"/>
-        <xs:attribute ref="pc:AssociationName"/>
-      </xs:complexType>
-    </xs:element>
-    <xs:attribute name="EntityNamespace" type="xs:string"/>
-    <xs:attribute name="EntityName" type="xs:string"/>
-    <xs:attribute name="SystemInstanceName" type="xs:string"/>
-    <xs:attribute name="AssociationName" type="xs:string"/>
-    <xs:element name="BDCEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
-          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
-          <xs:element ref="pc:EntityId1" minOccurs="0"/>
-          <xs:element ref="pc:EntityId2" minOccurs="0"/>
-          <xs:element ref="pc:EntityId3" minOccurs="0"/>
-          <xs:element ref="pc:EntityId4" minOccurs="0"/>
-          <xs:element ref="pc:EntityId5" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="EntityDisplayName" type="xs:string"/>
-    <xs:element name="EntityInstanceReference" type="xs:string"/>
-    <xs:element name="EntityId1" type="xs:string"/>
-    <xs:element name="EntityId2" type="xs:string"/>
-    <xs:element name="EntityId3" type="xs:string"/>
-    <xs:element name="EntityId4" type="xs:string"/>
-    <xs:element name="EntityId5" type="xs:string"/>
-    <xs:element name="Terms">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermInfo">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermName" minOccurs="0"/>
-          <xs:element ref="pc:TermId" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermName" type="xs:string"/>
-    <xs:element name="TermId" type="xs:string"/>
-  </xs:schema>
-</ct:contentTypeSchema>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="ae81e17b-11c2-44ae-89e9-9ad5f5ff8880">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1B067714-3971-4234-AABC-C408078E1CBC}"/>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2B0CDE59-B503-44BD-99FC-3772E552C782}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F1135BEA-392D-4B5C-B352-5EC7B079E2C0}"/>
 </file>
--- a/Atana-Backlog-AzureDevOps-v1.xlsx
+++ b/Atana-Backlog-AzureDevOps-v1.xlsx
@@ -5970,4 +5970,199 @@
   <autoFilter ref="A1:K48"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101008E3AE2BAD2C6FA4D8B4D95CE89FC31A3" ma:contentTypeVersion="8" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="a2ce85c62cd7e9a608298e998330aeb7">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="ae81e17b-11c2-44ae-89e9-9ad5f5ff8880" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="1504f635df8bfa7d9525024d2d10bc95" ns2:_="">
+    <xsd:import namespace="ae81e17b-11c2-44ae-89e9-9ad5f5ff8880"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="ae81e17b-11c2-44ae-89e9-9ad5f5ff8880" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="10" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="11" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="13" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="c4ac2493-9f1f-4345-86a0-c36146f38f1d" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="14" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="ae81e17b-11c2-44ae-89e9-9ad5f5ff8880">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9FCF4952-90D7-4639-A7F9-9CBD90F716E9}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9E80D158-3B3C-4F9B-87C9-79D352DD4D0E}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2A1B9623-98E2-401A-ACFB-0F826DAD5D3B}"/>
 </file>
--- a/Atana-Backlog-AzureDevOps-v1.xlsx
+++ b/Atana-Backlog-AzureDevOps-v1.xlsx
@@ -5970,199 +5970,4 @@
   <autoFilter ref="A1:K48"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101008E3AE2BAD2C6FA4D8B4D95CE89FC31A3" ma:contentTypeVersion="8" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="a2ce85c62cd7e9a608298e998330aeb7">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="ae81e17b-11c2-44ae-89e9-9ad5f5ff8880" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="1504f635df8bfa7d9525024d2d10bc95" ns2:_="">
-    <xsd:import namespace="ae81e17b-11c2-44ae-89e9-9ad5f5ff8880"/>
-    <xsd:element name="properties">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element name="documentManagement">
-            <xsd:complexType>
-              <xsd:all>
-                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
-              </xsd:all>
-            </xsd:complexType>
-          </xsd:element>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="ae81e17b-11c2-44ae-89e9-9ad5f5ff8880" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceSearchProperties" ma:index="10" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="11" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="13" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="c4ac2493-9f1f-4345-86a0-c36146f38f1d" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="14" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
-    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
-    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
-    <xsd:element name="coreProperties" type="CT_coreProperties"/>
-    <xsd:complexType name="CT_coreProperties">
-      <xsd:all>
-        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
-        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
-          <xsd:annotation>
-            <xsd:documentation>
-                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
-                    </xsd:documentation>
-          </xsd:annotation>
-        </xsd:element>
-        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-      </xsd:all>
-    </xsd:complexType>
-  </xsd:schema>
-  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
-    <xs:element name="Person">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:DisplayName" minOccurs="0"/>
-          <xs:element ref="pc:AccountId" minOccurs="0"/>
-          <xs:element ref="pc:AccountType" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="DisplayName" type="xs:string"/>
-    <xs:element name="AccountId" type="xs:string"/>
-    <xs:element name="AccountType" type="xs:string"/>
-    <xs:element name="BDCAssociatedEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-        <xs:attribute ref="pc:EntityNamespace"/>
-        <xs:attribute ref="pc:EntityName"/>
-        <xs:attribute ref="pc:SystemInstanceName"/>
-        <xs:attribute ref="pc:AssociationName"/>
-      </xs:complexType>
-    </xs:element>
-    <xs:attribute name="EntityNamespace" type="xs:string"/>
-    <xs:attribute name="EntityName" type="xs:string"/>
-    <xs:attribute name="SystemInstanceName" type="xs:string"/>
-    <xs:attribute name="AssociationName" type="xs:string"/>
-    <xs:element name="BDCEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
-          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
-          <xs:element ref="pc:EntityId1" minOccurs="0"/>
-          <xs:element ref="pc:EntityId2" minOccurs="0"/>
-          <xs:element ref="pc:EntityId3" minOccurs="0"/>
-          <xs:element ref="pc:EntityId4" minOccurs="0"/>
-          <xs:element ref="pc:EntityId5" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="EntityDisplayName" type="xs:string"/>
-    <xs:element name="EntityInstanceReference" type="xs:string"/>
-    <xs:element name="EntityId1" type="xs:string"/>
-    <xs:element name="EntityId2" type="xs:string"/>
-    <xs:element name="EntityId3" type="xs:string"/>
-    <xs:element name="EntityId4" type="xs:string"/>
-    <xs:element name="EntityId5" type="xs:string"/>
-    <xs:element name="Terms">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermInfo">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermName" minOccurs="0"/>
-          <xs:element ref="pc:TermId" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermName" type="xs:string"/>
-    <xs:element name="TermId" type="xs:string"/>
-  </xs:schema>
-</ct:contentTypeSchema>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="ae81e17b-11c2-44ae-89e9-9ad5f5ff8880">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9FCF4952-90D7-4639-A7F9-9CBD90F716E9}"/>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9E80D158-3B3C-4F9B-87C9-79D352DD4D0E}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2A1B9623-98E2-401A-ACFB-0F826DAD5D3B}"/>
 </file>
--- a/Atana-Backlog-AzureDevOps-v1.xlsx
+++ b/Atana-Backlog-AzureDevOps-v1.xlsx
@@ -5970,4 +5970,199 @@
   <autoFilter ref="A1:K48"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101008E3AE2BAD2C6FA4D8B4D95CE89FC31A3" ma:contentTypeVersion="8" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="a2ce85c62cd7e9a608298e998330aeb7">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="ae81e17b-11c2-44ae-89e9-9ad5f5ff8880" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="1504f635df8bfa7d9525024d2d10bc95" ns2:_="">
+    <xsd:import namespace="ae81e17b-11c2-44ae-89e9-9ad5f5ff8880"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="ae81e17b-11c2-44ae-89e9-9ad5f5ff8880" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="10" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="11" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="13" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="c4ac2493-9f1f-4345-86a0-c36146f38f1d" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="14" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="ae81e17b-11c2-44ae-89e9-9ad5f5ff8880">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{48987C77-3504-4521-A6B2-25227DD921EE}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EE27C49D-3B04-40D5-B5A5-B25D58C13DA8}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2CB87663-E449-4DEA-A391-FD153A0889A5}"/>
 </file>
--- a/Atana-Backlog-AzureDevOps-v1.xlsx
+++ b/Atana-Backlog-AzureDevOps-v1.xlsx
@@ -5970,199 +5970,4 @@
   <autoFilter ref="A1:K48"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101008E3AE2BAD2C6FA4D8B4D95CE89FC31A3" ma:contentTypeVersion="8" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="a2ce85c62cd7e9a608298e998330aeb7">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="ae81e17b-11c2-44ae-89e9-9ad5f5ff8880" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="1504f635df8bfa7d9525024d2d10bc95" ns2:_="">
-    <xsd:import namespace="ae81e17b-11c2-44ae-89e9-9ad5f5ff8880"/>
-    <xsd:element name="properties">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element name="documentManagement">
-            <xsd:complexType>
-              <xsd:all>
-                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
-              </xsd:all>
-            </xsd:complexType>
-          </xsd:element>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="ae81e17b-11c2-44ae-89e9-9ad5f5ff8880" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceSearchProperties" ma:index="10" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="11" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="13" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="c4ac2493-9f1f-4345-86a0-c36146f38f1d" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="14" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
-    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
-    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
-    <xsd:element name="coreProperties" type="CT_coreProperties"/>
-    <xsd:complexType name="CT_coreProperties">
-      <xsd:all>
-        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
-        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
-          <xsd:annotation>
-            <xsd:documentation>
-                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
-                    </xsd:documentation>
-          </xsd:annotation>
-        </xsd:element>
-        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-      </xsd:all>
-    </xsd:complexType>
-  </xsd:schema>
-  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
-    <xs:element name="Person">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:DisplayName" minOccurs="0"/>
-          <xs:element ref="pc:AccountId" minOccurs="0"/>
-          <xs:element ref="pc:AccountType" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="DisplayName" type="xs:string"/>
-    <xs:element name="AccountId" type="xs:string"/>
-    <xs:element name="AccountType" type="xs:string"/>
-    <xs:element name="BDCAssociatedEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-        <xs:attribute ref="pc:EntityNamespace"/>
-        <xs:attribute ref="pc:EntityName"/>
-        <xs:attribute ref="pc:SystemInstanceName"/>
-        <xs:attribute ref="pc:AssociationName"/>
-      </xs:complexType>
-    </xs:element>
-    <xs:attribute name="EntityNamespace" type="xs:string"/>
-    <xs:attribute name="EntityName" type="xs:string"/>
-    <xs:attribute name="SystemInstanceName" type="xs:string"/>
-    <xs:attribute name="AssociationName" type="xs:string"/>
-    <xs:element name="BDCEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
-          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
-          <xs:element ref="pc:EntityId1" minOccurs="0"/>
-          <xs:element ref="pc:EntityId2" minOccurs="0"/>
-          <xs:element ref="pc:EntityId3" minOccurs="0"/>
-          <xs:element ref="pc:EntityId4" minOccurs="0"/>
-          <xs:element ref="pc:EntityId5" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="EntityDisplayName" type="xs:string"/>
-    <xs:element name="EntityInstanceReference" type="xs:string"/>
-    <xs:element name="EntityId1" type="xs:string"/>
-    <xs:element name="EntityId2" type="xs:string"/>
-    <xs:element name="EntityId3" type="xs:string"/>
-    <xs:element name="EntityId4" type="xs:string"/>
-    <xs:element name="EntityId5" type="xs:string"/>
-    <xs:element name="Terms">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermInfo">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermName" minOccurs="0"/>
-          <xs:element ref="pc:TermId" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermName" type="xs:string"/>
-    <xs:element name="TermId" type="xs:string"/>
-  </xs:schema>
-</ct:contentTypeSchema>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="ae81e17b-11c2-44ae-89e9-9ad5f5ff8880">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{48987C77-3504-4521-A6B2-25227DD921EE}"/>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EE27C49D-3B04-40D5-B5A5-B25D58C13DA8}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2CB87663-E449-4DEA-A391-FD153A0889A5}"/>
 </file>
--- a/Atana-Backlog-AzureDevOps-v1.xlsx
+++ b/Atana-Backlog-AzureDevOps-v1.xlsx
@@ -5970,4 +5970,199 @@
   <autoFilter ref="A1:K48"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101008E3AE2BAD2C6FA4D8B4D95CE89FC31A3" ma:contentTypeVersion="8" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="a2ce85c62cd7e9a608298e998330aeb7">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="ae81e17b-11c2-44ae-89e9-9ad5f5ff8880" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="1504f635df8bfa7d9525024d2d10bc95" ns2:_="">
+    <xsd:import namespace="ae81e17b-11c2-44ae-89e9-9ad5f5ff8880"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="ae81e17b-11c2-44ae-89e9-9ad5f5ff8880" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="10" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="11" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="13" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="c4ac2493-9f1f-4345-86a0-c36146f38f1d" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="14" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="ae81e17b-11c2-44ae-89e9-9ad5f5ff8880">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A6A666F3-BB6E-42A7-BCE2-730E9480DC09}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0135219A-83C4-43BB-97FB-D801A23F88F6}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0DF412DD-4922-4440-9D48-B843D43380DA}"/>
 </file>
--- a/Atana-Backlog-AzureDevOps-v1.xlsx
+++ b/Atana-Backlog-AzureDevOps-v1.xlsx
@@ -5970,199 +5970,4 @@
   <autoFilter ref="A1:K48"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101008E3AE2BAD2C6FA4D8B4D95CE89FC31A3" ma:contentTypeVersion="8" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="a2ce85c62cd7e9a608298e998330aeb7">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="ae81e17b-11c2-44ae-89e9-9ad5f5ff8880" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="1504f635df8bfa7d9525024d2d10bc95" ns2:_="">
-    <xsd:import namespace="ae81e17b-11c2-44ae-89e9-9ad5f5ff8880"/>
-    <xsd:element name="properties">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element name="documentManagement">
-            <xsd:complexType>
-              <xsd:all>
-                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
-              </xsd:all>
-            </xsd:complexType>
-          </xsd:element>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="ae81e17b-11c2-44ae-89e9-9ad5f5ff8880" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceSearchProperties" ma:index="10" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="11" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="13" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="c4ac2493-9f1f-4345-86a0-c36146f38f1d" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="14" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
-    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
-    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
-    <xsd:element name="coreProperties" type="CT_coreProperties"/>
-    <xsd:complexType name="CT_coreProperties">
-      <xsd:all>
-        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
-        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
-          <xsd:annotation>
-            <xsd:documentation>
-                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
-                    </xsd:documentation>
-          </xsd:annotation>
-        </xsd:element>
-        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-      </xsd:all>
-    </xsd:complexType>
-  </xsd:schema>
-  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
-    <xs:element name="Person">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:DisplayName" minOccurs="0"/>
-          <xs:element ref="pc:AccountId" minOccurs="0"/>
-          <xs:element ref="pc:AccountType" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="DisplayName" type="xs:string"/>
-    <xs:element name="AccountId" type="xs:string"/>
-    <xs:element name="AccountType" type="xs:string"/>
-    <xs:element name="BDCAssociatedEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-        <xs:attribute ref="pc:EntityNamespace"/>
-        <xs:attribute ref="pc:EntityName"/>
-        <xs:attribute ref="pc:SystemInstanceName"/>
-        <xs:attribute ref="pc:AssociationName"/>
-      </xs:complexType>
-    </xs:element>
-    <xs:attribute name="EntityNamespace" type="xs:string"/>
-    <xs:attribute name="EntityName" type="xs:string"/>
-    <xs:attribute name="SystemInstanceName" type="xs:string"/>
-    <xs:attribute name="AssociationName" type="xs:string"/>
-    <xs:element name="BDCEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
-          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
-          <xs:element ref="pc:EntityId1" minOccurs="0"/>
-          <xs:element ref="pc:EntityId2" minOccurs="0"/>
-          <xs:element ref="pc:EntityId3" minOccurs="0"/>
-          <xs:element ref="pc:EntityId4" minOccurs="0"/>
-          <xs:element ref="pc:EntityId5" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="EntityDisplayName" type="xs:string"/>
-    <xs:element name="EntityInstanceReference" type="xs:string"/>
-    <xs:element name="EntityId1" type="xs:string"/>
-    <xs:element name="EntityId2" type="xs:string"/>
-    <xs:element name="EntityId3" type="xs:string"/>
-    <xs:element name="EntityId4" type="xs:string"/>
-    <xs:element name="EntityId5" type="xs:string"/>
-    <xs:element name="Terms">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermInfo">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermName" minOccurs="0"/>
-          <xs:element ref="pc:TermId" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermName" type="xs:string"/>
-    <xs:element name="TermId" type="xs:string"/>
-  </xs:schema>
-</ct:contentTypeSchema>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="ae81e17b-11c2-44ae-89e9-9ad5f5ff8880">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A6A666F3-BB6E-42A7-BCE2-730E9480DC09}"/>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0135219A-83C4-43BB-97FB-D801A23F88F6}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0DF412DD-4922-4440-9D48-B843D43380DA}"/>
 </file>
--- a/Atana-Backlog-AzureDevOps-v1.xlsx
+++ b/Atana-Backlog-AzureDevOps-v1.xlsx
@@ -5970,4 +5970,199 @@
   <autoFilter ref="A1:K48"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101008E3AE2BAD2C6FA4D8B4D95CE89FC31A3" ma:contentTypeVersion="8" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="a2ce85c62cd7e9a608298e998330aeb7">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="ae81e17b-11c2-44ae-89e9-9ad5f5ff8880" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="1504f635df8bfa7d9525024d2d10bc95" ns2:_="">
+    <xsd:import namespace="ae81e17b-11c2-44ae-89e9-9ad5f5ff8880"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="ae81e17b-11c2-44ae-89e9-9ad5f5ff8880" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="10" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="11" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="13" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="c4ac2493-9f1f-4345-86a0-c36146f38f1d" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="14" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="ae81e17b-11c2-44ae-89e9-9ad5f5ff8880">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CD6D609D-7AE7-40C9-B6A2-1065764282AA}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5F43B79D-A75A-42E9-950D-5A9DE5311A4B}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7209F935-EC4A-4070-AD36-1948755B4176}"/>
 </file>
--- a/Atana-Backlog-AzureDevOps-v1.xlsx
+++ b/Atana-Backlog-AzureDevOps-v1.xlsx
@@ -5970,199 +5970,4 @@
   <autoFilter ref="A1:K48"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101008E3AE2BAD2C6FA4D8B4D95CE89FC31A3" ma:contentTypeVersion="8" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="a2ce85c62cd7e9a608298e998330aeb7">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="ae81e17b-11c2-44ae-89e9-9ad5f5ff8880" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="1504f635df8bfa7d9525024d2d10bc95" ns2:_="">
-    <xsd:import namespace="ae81e17b-11c2-44ae-89e9-9ad5f5ff8880"/>
-    <xsd:element name="properties">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element name="documentManagement">
-            <xsd:complexType>
-              <xsd:all>
-                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
-              </xsd:all>
-            </xsd:complexType>
-          </xsd:element>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="ae81e17b-11c2-44ae-89e9-9ad5f5ff8880" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceSearchProperties" ma:index="10" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="11" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="13" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="c4ac2493-9f1f-4345-86a0-c36146f38f1d" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="14" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
-    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
-    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
-    <xsd:element name="coreProperties" type="CT_coreProperties"/>
-    <xsd:complexType name="CT_coreProperties">
-      <xsd:all>
-        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
-        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
-          <xsd:annotation>
-            <xsd:documentation>
-                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
-                    </xsd:documentation>
-          </xsd:annotation>
-        </xsd:element>
-        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-      </xsd:all>
-    </xsd:complexType>
-  </xsd:schema>
-  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
-    <xs:element name="Person">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:DisplayName" minOccurs="0"/>
-          <xs:element ref="pc:AccountId" minOccurs="0"/>
-          <xs:element ref="pc:AccountType" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="DisplayName" type="xs:string"/>
-    <xs:element name="AccountId" type="xs:string"/>
-    <xs:element name="AccountType" type="xs:string"/>
-    <xs:element name="BDCAssociatedEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-        <xs:attribute ref="pc:EntityNamespace"/>
-        <xs:attribute ref="pc:EntityName"/>
-        <xs:attribute ref="pc:SystemInstanceName"/>
-        <xs:attribute ref="pc:AssociationName"/>
-      </xs:complexType>
-    </xs:element>
-    <xs:attribute name="EntityNamespace" type="xs:string"/>
-    <xs:attribute name="EntityName" type="xs:string"/>
-    <xs:attribute name="SystemInstanceName" type="xs:string"/>
-    <xs:attribute name="AssociationName" type="xs:string"/>
-    <xs:element name="BDCEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
-          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
-          <xs:element ref="pc:EntityId1" minOccurs="0"/>
-          <xs:element ref="pc:EntityId2" minOccurs="0"/>
-          <xs:element ref="pc:EntityId3" minOccurs="0"/>
-          <xs:element ref="pc:EntityId4" minOccurs="0"/>
-          <xs:element ref="pc:EntityId5" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="EntityDisplayName" type="xs:string"/>
-    <xs:element name="EntityInstanceReference" type="xs:string"/>
-    <xs:element name="EntityId1" type="xs:string"/>
-    <xs:element name="EntityId2" type="xs:string"/>
-    <xs:element name="EntityId3" type="xs:string"/>
-    <xs:element name="EntityId4" type="xs:string"/>
-    <xs:element name="EntityId5" type="xs:string"/>
-    <xs:element name="Terms">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermInfo">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermName" minOccurs="0"/>
-          <xs:element ref="pc:TermId" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermName" type="xs:string"/>
-    <xs:element name="TermId" type="xs:string"/>
-  </xs:schema>
-</ct:contentTypeSchema>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="ae81e17b-11c2-44ae-89e9-9ad5f5ff8880">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CD6D609D-7AE7-40C9-B6A2-1065764282AA}"/>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5F43B79D-A75A-42E9-950D-5A9DE5311A4B}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7209F935-EC4A-4070-AD36-1948755B4176}"/>
 </file>
--- a/Atana-Backlog-AzureDevOps-v1.xlsx
+++ b/Atana-Backlog-AzureDevOps-v1.xlsx
@@ -5970,4 +5970,199 @@
   <autoFilter ref="A1:K48"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101008E3AE2BAD2C6FA4D8B4D95CE89FC31A3" ma:contentTypeVersion="8" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="a2ce85c62cd7e9a608298e998330aeb7">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="ae81e17b-11c2-44ae-89e9-9ad5f5ff8880" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="1504f635df8bfa7d9525024d2d10bc95" ns2:_="">
+    <xsd:import namespace="ae81e17b-11c2-44ae-89e9-9ad5f5ff8880"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="ae81e17b-11c2-44ae-89e9-9ad5f5ff8880" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="10" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="11" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="13" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="c4ac2493-9f1f-4345-86a0-c36146f38f1d" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="14" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="ae81e17b-11c2-44ae-89e9-9ad5f5ff8880">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CF2F20AB-FC0D-4F93-85DF-C23B3F9C6C01}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{25D2A1CD-B4EA-4F4F-BA71-1FA55CD3F983}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{573F944A-E6D2-4F7D-9186-B9B824E60B80}"/>
 </file>
--- a/Atana-Backlog-AzureDevOps-v1.xlsx
+++ b/Atana-Backlog-AzureDevOps-v1.xlsx
@@ -5970,199 +5970,4 @@
   <autoFilter ref="A1:K48"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101008E3AE2BAD2C6FA4D8B4D95CE89FC31A3" ma:contentTypeVersion="8" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="a2ce85c62cd7e9a608298e998330aeb7">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="ae81e17b-11c2-44ae-89e9-9ad5f5ff8880" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="1504f635df8bfa7d9525024d2d10bc95" ns2:_="">
-    <xsd:import namespace="ae81e17b-11c2-44ae-89e9-9ad5f5ff8880"/>
-    <xsd:element name="properties">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element name="documentManagement">
-            <xsd:complexType>
-              <xsd:all>
-                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
-              </xsd:all>
-            </xsd:complexType>
-          </xsd:element>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="ae81e17b-11c2-44ae-89e9-9ad5f5ff8880" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceSearchProperties" ma:index="10" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="11" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="13" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="c4ac2493-9f1f-4345-86a0-c36146f38f1d" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="14" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
-    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
-    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
-    <xsd:element name="coreProperties" type="CT_coreProperties"/>
-    <xsd:complexType name="CT_coreProperties">
-      <xsd:all>
-        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
-        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
-          <xsd:annotation>
-            <xsd:documentation>
-                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
-                    </xsd:documentation>
-          </xsd:annotation>
-        </xsd:element>
-        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-      </xsd:all>
-    </xsd:complexType>
-  </xsd:schema>
-  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
-    <xs:element name="Person">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:DisplayName" minOccurs="0"/>
-          <xs:element ref="pc:AccountId" minOccurs="0"/>
-          <xs:element ref="pc:AccountType" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="DisplayName" type="xs:string"/>
-    <xs:element name="AccountId" type="xs:string"/>
-    <xs:element name="AccountType" type="xs:string"/>
-    <xs:element name="BDCAssociatedEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-        <xs:attribute ref="pc:EntityNamespace"/>
-        <xs:attribute ref="pc:EntityName"/>
-        <xs:attribute ref="pc:SystemInstanceName"/>
-        <xs:attribute ref="pc:AssociationName"/>
-      </xs:complexType>
-    </xs:element>
-    <xs:attribute name="EntityNamespace" type="xs:string"/>
-    <xs:attribute name="EntityName" type="xs:string"/>
-    <xs:attribute name="SystemInstanceName" type="xs:string"/>
-    <xs:attribute name="AssociationName" type="xs:string"/>
-    <xs:element name="BDCEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
-          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
-          <xs:element ref="pc:EntityId1" minOccurs="0"/>
-          <xs:element ref="pc:EntityId2" minOccurs="0"/>
-          <xs:element ref="pc:EntityId3" minOccurs="0"/>
-          <xs:element ref="pc:EntityId4" minOccurs="0"/>
-          <xs:element ref="pc:EntityId5" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="EntityDisplayName" type="xs:string"/>
-    <xs:element name="EntityInstanceReference" type="xs:string"/>
-    <xs:element name="EntityId1" type="xs:string"/>
-    <xs:element name="EntityId2" type="xs:string"/>
-    <xs:element name="EntityId3" type="xs:string"/>
-    <xs:element name="EntityId4" type="xs:string"/>
-    <xs:element name="EntityId5" type="xs:string"/>
-    <xs:element name="Terms">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermInfo">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermName" minOccurs="0"/>
-          <xs:element ref="pc:TermId" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermName" type="xs:string"/>
-    <xs:element name="TermId" type="xs:string"/>
-  </xs:schema>
-</ct:contentTypeSchema>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="ae81e17b-11c2-44ae-89e9-9ad5f5ff8880">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CF2F20AB-FC0D-4F93-85DF-C23B3F9C6C01}"/>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{25D2A1CD-B4EA-4F4F-BA71-1FA55CD3F983}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{573F944A-E6D2-4F7D-9186-B9B824E60B80}"/>
 </file>
--- a/Atana-Backlog-AzureDevOps-v1.xlsx
+++ b/Atana-Backlog-AzureDevOps-v1.xlsx
@@ -5970,4 +5970,199 @@
   <autoFilter ref="A1:K48"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101008E3AE2BAD2C6FA4D8B4D95CE89FC31A3" ma:contentTypeVersion="8" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="a2ce85c62cd7e9a608298e998330aeb7">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="ae81e17b-11c2-44ae-89e9-9ad5f5ff8880" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="1504f635df8bfa7d9525024d2d10bc95" ns2:_="">
+    <xsd:import namespace="ae81e17b-11c2-44ae-89e9-9ad5f5ff8880"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="ae81e17b-11c2-44ae-89e9-9ad5f5ff8880" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="10" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="11" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="13" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="c4ac2493-9f1f-4345-86a0-c36146f38f1d" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="14" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="ae81e17b-11c2-44ae-89e9-9ad5f5ff8880">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{88EB7C6B-5120-413F-8106-F74F828AAF9A}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{ED2A7635-AF7C-4A38-9A60-76C9BBF97359}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E72D3A3D-DDB5-422E-9275-3C749A020B3A}"/>
 </file>
--- a/Atana-Backlog-AzureDevOps-v1.xlsx
+++ b/Atana-Backlog-AzureDevOps-v1.xlsx
@@ -5970,199 +5970,4 @@
   <autoFilter ref="A1:K48"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101008E3AE2BAD2C6FA4D8B4D95CE89FC31A3" ma:contentTypeVersion="8" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="a2ce85c62cd7e9a608298e998330aeb7">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="ae81e17b-11c2-44ae-89e9-9ad5f5ff8880" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="1504f635df8bfa7d9525024d2d10bc95" ns2:_="">
-    <xsd:import namespace="ae81e17b-11c2-44ae-89e9-9ad5f5ff8880"/>
-    <xsd:element name="properties">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element name="documentManagement">
-            <xsd:complexType>
-              <xsd:all>
-                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
-              </xsd:all>
-            </xsd:complexType>
-          </xsd:element>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="ae81e17b-11c2-44ae-89e9-9ad5f5ff8880" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceSearchProperties" ma:index="10" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="11" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="13" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="c4ac2493-9f1f-4345-86a0-c36146f38f1d" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="14" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
-    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
-    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
-    <xsd:element name="coreProperties" type="CT_coreProperties"/>
-    <xsd:complexType name="CT_coreProperties">
-      <xsd:all>
-        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
-        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
-          <xsd:annotation>
-            <xsd:documentation>
-                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
-                    </xsd:documentation>
-          </xsd:annotation>
-        </xsd:element>
-        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-      </xsd:all>
-    </xsd:complexType>
-  </xsd:schema>
-  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
-    <xs:element name="Person">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:DisplayName" minOccurs="0"/>
-          <xs:element ref="pc:AccountId" minOccurs="0"/>
-          <xs:element ref="pc:AccountType" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="DisplayName" type="xs:string"/>
-    <xs:element name="AccountId" type="xs:string"/>
-    <xs:element name="AccountType" type="xs:string"/>
-    <xs:element name="BDCAssociatedEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-        <xs:attribute ref="pc:EntityNamespace"/>
-        <xs:attribute ref="pc:EntityName"/>
-        <xs:attribute ref="pc:SystemInstanceName"/>
-        <xs:attribute ref="pc:AssociationName"/>
-      </xs:complexType>
-    </xs:element>
-    <xs:attribute name="EntityNamespace" type="xs:string"/>
-    <xs:attribute name="EntityName" type="xs:string"/>
-    <xs:attribute name="SystemInstanceName" type="xs:string"/>
-    <xs:attribute name="AssociationName" type="xs:string"/>
-    <xs:element name="BDCEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
-          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
-          <xs:element ref="pc:EntityId1" minOccurs="0"/>
-          <xs:element ref="pc:EntityId2" minOccurs="0"/>
-          <xs:element ref="pc:EntityId3" minOccurs="0"/>
-          <xs:element ref="pc:EntityId4" minOccurs="0"/>
-          <xs:element ref="pc:EntityId5" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="EntityDisplayName" type="xs:string"/>
-    <xs:element name="EntityInstanceReference" type="xs:string"/>
-    <xs:element name="EntityId1" type="xs:string"/>
-    <xs:element name="EntityId2" type="xs:string"/>
-    <xs:element name="EntityId3" type="xs:string"/>
-    <xs:element name="EntityId4" type="xs:string"/>
-    <xs:element name="EntityId5" type="xs:string"/>
-    <xs:element name="Terms">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermInfo">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermName" minOccurs="0"/>
-          <xs:element ref="pc:TermId" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermName" type="xs:string"/>
-    <xs:element name="TermId" type="xs:string"/>
-  </xs:schema>
-</ct:contentTypeSchema>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="ae81e17b-11c2-44ae-89e9-9ad5f5ff8880">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{88EB7C6B-5120-413F-8106-F74F828AAF9A}"/>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{ED2A7635-AF7C-4A38-9A60-76C9BBF97359}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E72D3A3D-DDB5-422E-9275-3C749A020B3A}"/>
 </file>